--- a/162.xlsx
+++ b/162.xlsx
@@ -511,7 +511,7 @@
         <v>1.899414658546448</v>
       </c>
       <c r="K2" t="n">
-        <v>1.225789999807603e-05</v>
+        <v>1.109919999998965e-05</v>
       </c>
     </row>
     <row r="3">
@@ -552,7 +552,7 @@
         <v>2.021719694137573</v>
       </c>
       <c r="K3" t="n">
-        <v>7.28049999815994e-06</v>
+        <v>7.339300000239746e-06</v>
       </c>
     </row>
     <row r="4">
@@ -593,7 +593,7 @@
         <v>2.23393440246582</v>
       </c>
       <c r="K4" t="n">
-        <v>7.285700001375517e-06</v>
+        <v>7.33349999973143e-06</v>
       </c>
     </row>
     <row r="5">
@@ -634,7 +634,7 @@
         <v>1.836353302001953</v>
       </c>
       <c r="K5" t="n">
-        <v>8.117500001389999e-06</v>
+        <v>7.124400000066089e-06</v>
       </c>
     </row>
     <row r="6">
@@ -675,7 +675,7 @@
         <v>2.534233093261719</v>
       </c>
       <c r="K6" t="n">
-        <v>7.508099999540719e-06</v>
+        <v>7.877100000769133e-06</v>
       </c>
     </row>
     <row r="7">
@@ -716,7 +716,7 @@
         <v>0.6462885141372681</v>
       </c>
       <c r="K7" t="n">
-        <v>7.752800000162096e-06</v>
+        <v>7.241100000101142e-06</v>
       </c>
     </row>
     <row r="8">
@@ -757,7 +757,7 @@
         <v>0.6290862560272217</v>
       </c>
       <c r="K8" t="n">
-        <v>7.974199997988762e-06</v>
+        <v>6.924399999661546e-06</v>
       </c>
     </row>
     <row r="9">
@@ -798,7 +798,7 @@
         <v>0.6569992899894714</v>
       </c>
       <c r="K9" t="n">
-        <v>8.16829999894253e-06</v>
+        <v>7.144999999582069e-06</v>
       </c>
     </row>
     <row r="10">
@@ -839,7 +839,7 @@
         <v>0.6297457814216614</v>
       </c>
       <c r="K10" t="n">
-        <v>7.488600000215228e-06</v>
+        <v>6.860399999823131e-06</v>
       </c>
     </row>
     <row r="11">
@@ -880,7 +880,7 @@
         <v>0.612906277179718</v>
       </c>
       <c r="K11" t="n">
-        <v>8.544199998141266e-06</v>
+        <v>7.44600000052742e-06</v>
       </c>
     </row>
     <row r="12">
@@ -921,7 +921,7 @@
         <v>0.6798930764198303</v>
       </c>
       <c r="K12" t="n">
-        <v>7.581799996842165e-06</v>
+        <v>7.245599999805563e-06</v>
       </c>
     </row>
     <row r="13">
@@ -962,7 +962,7 @@
         <v>0.6647471785545349</v>
       </c>
       <c r="K13" t="n">
-        <v>7.887299998401432e-06</v>
+        <v>7.193899999947462e-06</v>
       </c>
     </row>
     <row r="14">
@@ -1003,7 +1003,7 @@
         <v>0.6927752494812012</v>
       </c>
       <c r="K14" t="n">
-        <v>7.399699999950826e-06</v>
+        <v>7.049400000141759e-06</v>
       </c>
     </row>
     <row r="15">
@@ -1044,7 +1044,7 @@
         <v>0.6775802373886108</v>
       </c>
       <c r="K15" t="n">
-        <v>8.396599998377497e-06</v>
+        <v>7.191400000010617e-06</v>
       </c>
     </row>
     <row r="16">
@@ -1085,7 +1085,7 @@
         <v>0.6975191235542297</v>
       </c>
       <c r="K16" t="n">
-        <v>7.088900001690491e-06</v>
+        <v>1.520700000037323e-05</v>
       </c>
     </row>
     <row r="17">
@@ -1126,7 +1126,7 @@
         <v>0.8259356021881104</v>
       </c>
       <c r="K17" t="n">
-        <v>1.466119999895454e-05</v>
+        <v>1.396999999997206e-05</v>
       </c>
     </row>
     <row r="18">
@@ -1167,7 +1167,7 @@
         <v>0.7692122459411621</v>
       </c>
       <c r="K18" t="n">
-        <v>1.415869999982533e-05</v>
+        <v>1.390829999945709e-05</v>
       </c>
     </row>
     <row r="19">
@@ -1208,7 +1208,7 @@
         <v>0.7609123587608337</v>
       </c>
       <c r="K19" t="n">
-        <v>1.643779999722028e-05</v>
+        <v>1.357180000013614e-05</v>
       </c>
     </row>
     <row r="20">
@@ -1249,7 +1249,7 @@
         <v>0.8261111378669739</v>
       </c>
       <c r="K20" t="n">
-        <v>1.817170000140322e-05</v>
+        <v>1.402340000004187e-05</v>
       </c>
     </row>
     <row r="21">
@@ -1290,7 +1290,7 @@
         <v>0.7763814330101013</v>
       </c>
       <c r="K21" t="n">
-        <v>1.356210000085412e-05</v>
+        <v>1.332749999983207e-05</v>
       </c>
     </row>
     <row r="22">
@@ -1331,7 +1331,7 @@
         <v>0.6375079751014709</v>
       </c>
       <c r="K22" t="n">
-        <v>1.349859999754699e-05</v>
+        <v>1.352979999956005e-05</v>
       </c>
     </row>
     <row r="23">
@@ -1372,7 +1372,7 @@
         <v>0.6591068506240845</v>
       </c>
       <c r="K23" t="n">
-        <v>1.472730000023148e-05</v>
+        <v>1.372150000042893e-05</v>
       </c>
     </row>
     <row r="24">
@@ -1413,7 +1413,7 @@
         <v>0.6344265937805176</v>
       </c>
       <c r="K24" t="n">
-        <v>1.535030000013649e-05</v>
+        <v>1.388169999972888e-05</v>
       </c>
     </row>
     <row r="25">
@@ -1454,7 +1454,7 @@
         <v>0.7032672762870789</v>
       </c>
       <c r="K25" t="n">
-        <v>1.340669999990496e-05</v>
+        <v>1.375490000009449e-05</v>
       </c>
     </row>
     <row r="26">
@@ -1495,7 +1495,7 @@
         <v>0.7030646800994873</v>
       </c>
       <c r="K26" t="n">
-        <v>1.47992999991402e-05</v>
+        <v>1.35126000004675e-05</v>
       </c>
     </row>
   </sheetData>
